--- a/data/trans_bre/P32C-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Edad-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,21</t>
+          <t>-3,8; 1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,19</t>
+          <t>-4,09; -0,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,39</t>
+          <t>-3,76; -0,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 13,36</t>
+          <t>0,16; 12,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,67</t>
+          <t>-100,0; 128,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 98,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,49</t>
+          <t>-2,55; 2,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,78</t>
+          <t>-3,37; -0,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,9</t>
+          <t>-2,58; 1,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,12; 223,43</t>
+          <t>-100,0; 193,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,96</t>
+          <t>-100,0; 217,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,33</t>
+          <t>-1,26; 1,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -1,3</t>
+          <t>-4,26; -1,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,24</t>
+          <t>-2,69; -0,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,7</t>
+          <t>-2,12; 1,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,54</t>
+          <t>-2,29; 1,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -1,08</t>
+          <t>-4,87; -1,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,85</t>
+          <t>-1,57; 2,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,28</t>
+          <t>-2,42; -0,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -1,49</t>
+          <t>-6,66; -1,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,47</t>
+          <t>-1,3; 4,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -1,19</t>
+          <t>-5,72; -1,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,54</t>
+          <t>-3,21; 1,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 158,16</t>
+          <t>-86,32; 154,54</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,0</t>
+          <t>-3,04; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -0,64</t>
+          <t>-6,14; -0,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,53</t>
+          <t>-4,66; -0,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,5; -0,07</t>
+          <t>-3,63; -0,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -1,1</t>
+          <t>-10,02; -1,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 0,0</t>
+          <t>-6,82; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 4,95</t>
+          <t>-3,69; 4,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,04</t>
+          <t>-1,78; 0,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -1,02</t>
+          <t>-2,55; -1,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; -0,32</t>
+          <t>-1,75; -0,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,82</t>
+          <t>-1,13; 0,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,15; 8,69</t>
+          <t>-81,61; 11,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-96,28; -53,5</t>
+          <t>-96,19; -54,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-86,06; -15,6</t>
+          <t>-88,16; -18,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 93,38</t>
+          <t>-72,37; 69,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32C-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,22</t>
+          <t>-4,11; 1,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,02</t>
+          <t>-3,85; 0,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -0,38</t>
+          <t>-3,8; -0,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 12,7</t>
+          <t>1,51; 14,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 128,99</t>
+          <t>-100,0; 152,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,14</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,48</t>
+          <t>-2,53; 2,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,78</t>
+          <t>-3,65; -0,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,81</t>
+          <t>-2,54; 1,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 193,56</t>
+          <t>-100,0; 249,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,68</t>
+          <t>-100,0; 207,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-29,44%</t>
+          <t>-31,84%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,13</t>
+          <t>-1,43; 0,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -1,36</t>
+          <t>-4,41; -1,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,24</t>
+          <t>-2,82; -0,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,38</t>
+          <t>-1,87; 1,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,79</t>
+          <t>-2,34; 1,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,87; -1,11</t>
+          <t>-5,19; -1,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,11</t>
+          <t>-1,49; 2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,25</t>
+          <t>-2,86; -0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 652,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-35,35%</t>
+          <t>-32,25%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -1,5</t>
+          <t>-6,73; -1,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,77</t>
+          <t>-1,56; 4,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -1,21</t>
+          <t>-5,54; -1,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,5</t>
+          <t>-3,05; 1,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-86,32; 154,54</t>
+          <t>-87,45; 207,4</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-90,0%</t>
+          <t>-62,62%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,0</t>
+          <t>-2,59; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -0,65</t>
+          <t>-5,72; -0,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -0,53</t>
+          <t>-5,17; -0,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,63; -0,26</t>
+          <t>-2,67; 0,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-36,6%</t>
+          <t>-37,24%</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; -1,07</t>
+          <t>-9,87; -1,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 0,0</t>
+          <t>-6,75; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 4,54</t>
+          <t>-3,66; 4,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-24,41%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,06</t>
+          <t>-1,81; 0,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -1,07</t>
+          <t>-2,52; -1,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,36</t>
+          <t>-1,79; -0,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,65</t>
+          <t>-0,76; 1,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 11,63</t>
+          <t>-78,91; 16,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-96,19; -54,77</t>
+          <t>-100,0; -57,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-88,16; -18,34</t>
+          <t>-88,23; -26,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-72,37; 69,4</t>
+          <t>-56,96; 148,62</t>
         </is>
       </c>
     </row>
